--- a/PTBR/Lang/PTBR/Game/Game.xlsx
+++ b/PTBR/Lang/PTBR/Game/Game.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1003"/>
+  <dimension ref="A1:F1006"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col collapsed="1" width="16" customWidth="1" min="1" max="1"/>
@@ -23363,22 +23363,22 @@
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>Alpha 20.64</t>
+          <t>EA 23.285</t>
         </is>
       </c>
       <c r="D803" t="inlineStr">
         <is>
-          <t xml:space="preserve"> • 「Você açoita #1 com #2」 •</t>
+          <t>#1 chicote(s) #2 com #3.</t>
         </is>
       </c>
       <c r="E803" t="inlineStr">
         <is>
-          <t>You whip #1 with #2.</t>
+          <t>#1 whip(s) #2 with #3.</t>
         </is>
       </c>
       <c r="F803" t="inlineStr">
         <is>
-          <t>あなたは#2で#1を打った。</t>
+          <t>#1は#3で#2を打った。</t>
         </is>
       </c>
     </row>
@@ -28411,34 +28411,34 @@
     <row r="988">
       <c r="A988" t="inlineStr">
         <is>
-          <t>self_dupe</t>
+          <t>cat_migration</t>
         </is>
       </c>
       <c r="B988" t="inlineStr">
         <is>
-          <t>EA 23.207</t>
+          <t>EA 23.285</t>
         </is>
       </c>
       <c r="D988" t="inlineStr">
         <is>
-          <t>#1 monta(m) #2.</t>
+          <t>#1 Gato(s) Prateado(s) parte(m) em busca de um novo lar.</t>
         </is>
       </c>
       <c r="E988" t="inlineStr">
         <is>
-          <t>#1 assemble(s) #2.</t>
+          <t>#1 Silver Cats/Cat depart(s) in search of a new home.</t>
         </is>
       </c>
       <c r="F988" t="inlineStr">
         <is>
-          <t>#1は#2を組み立てた。</t>
+          <t>#1匹のシルバーキャット達は新天地を求めて旅立っていった。</t>
         </is>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="inlineStr">
         <is>
-          <t>update_deepest</t>
+          <t>self_dupe</t>
         </is>
       </c>
       <c r="B989" t="inlineStr">
@@ -28448,105 +28448,105 @@
       </c>
       <c r="D989" t="inlineStr">
         <is>
-          <t>O nível mais profundo alcançado foi atualizado para #1.</t>
+          <t>#1 monta(m) #2.</t>
         </is>
       </c>
       <c r="E989" t="inlineStr">
         <is>
-          <t>The deepest reached level has been updated to #1.</t>
+          <t>#1 assemble(s) #2.</t>
         </is>
       </c>
       <c r="F989" t="inlineStr">
         <is>
-          <t>最深到達層が#1階に更新された。</t>
+          <t>#1は#2を組み立てた。</t>
         </is>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="inlineStr">
         <is>
-          <t>update_deepest_void</t>
+          <t>update_deepest</t>
         </is>
       </c>
       <c r="B990" t="inlineStr">
         <is>
-          <t>EA 23.209</t>
+          <t>EA 23.207</t>
         </is>
       </c>
       <c r="D990" t="inlineStr">
         <is>
-          <t>O nível mais profundo alcançado do Vazio foi atualizado para #1.</t>
+          <t>O nível mais profundo alcançado foi atualizado para #1.</t>
         </is>
       </c>
       <c r="E990" t="inlineStr">
         <is>
-          <t>The deepest reached level of the Void has been updated to #1.</t>
+          <t>The deepest reached level has been updated to #1.</t>
         </is>
       </c>
       <c r="F990" t="inlineStr">
         <is>
-          <t>すくつの最深到達層が#1階に更新された。</t>
+          <t>最深到達層が#1階に更新された。</t>
         </is>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="inlineStr">
         <is>
-          <t>transform_seen</t>
+          <t>update_deepest_void</t>
         </is>
       </c>
       <c r="B991" t="inlineStr">
         <is>
-          <t>EA 23.245</t>
+          <t>EA 23.209</t>
         </is>
       </c>
       <c r="D991" t="inlineStr">
         <is>
-          <t>Alguém descobre quem #1 realmente é(são)!</t>
+          <t>O nível mais profundo alcançado do Vazio foi atualizado para #1.</t>
         </is>
       </c>
       <c r="E991" t="inlineStr">
         <is>
-          <t>Someone figures out who #1 really are/is!</t>
+          <t>The deepest reached level of the Void has been updated to #1.</t>
         </is>
       </c>
       <c r="F991" t="inlineStr">
         <is>
-          <t>誰かが#1の正体に気づいた！</t>
+          <t>すくつの最深到達層が#1階に更新された。</t>
         </is>
       </c>
     </row>
     <row r="992">
       <c r="A992" t="inlineStr">
         <is>
-          <t>egghatch</t>
+          <t>transform_seen</t>
         </is>
       </c>
       <c r="B992" t="inlineStr">
         <is>
-          <t>EA 23.246</t>
+          <t>EA 23.245</t>
         </is>
       </c>
       <c r="D992" t="inlineStr">
         <is>
-          <t>Um casulo se abre e algo rasteja para fora.</t>
+          <t>Alguém descobre quem #1 realmente é(são)!</t>
         </is>
       </c>
       <c r="E992" t="inlineStr">
         <is>
-          <t>A cocoon splits open as something crawls out.</t>
+          <t>Someone figures out who #1 really are/is!</t>
         </is>
       </c>
       <c r="F992" t="inlineStr">
         <is>
-          <t>コクーンの殻を破り何かが這い出した。</t>
+          <t>誰かが#1の正体に気づいた！</t>
         </is>
       </c>
     </row>
     <row r="993">
       <c r="A993" t="inlineStr">
         <is>
-          <t>egglay</t>
+          <t>egghatch</t>
         </is>
       </c>
       <c r="B993" t="inlineStr">
@@ -28556,105 +28556,105 @@
       </c>
       <c r="D993" t="inlineStr">
         <is>
-          <t>#1 treme(m) seu abdômen e libera(m) um casulo pegajoso.</t>
+          <t>Um casulo se abre e algo rasteja para fora.</t>
         </is>
       </c>
       <c r="E993" t="inlineStr">
         <is>
-          <t>#1 tremble(s) its abdomen and release(s) a sticky cocoon.</t>
+          <t>A cocoon splits open as something crawls out.</t>
         </is>
       </c>
       <c r="F993" t="inlineStr">
         <is>
-          <t>#1は腹を震わせ粘りつく卵塊を産み落とした。</t>
+          <t>コクーンの殻を破り何かが這い出した。</t>
         </is>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="inlineStr">
         <is>
-          <t>negateCondition</t>
+          <t>egglay</t>
         </is>
       </c>
       <c r="B994" t="inlineStr">
         <is>
-          <t>EA 23.247</t>
+          <t>EA 23.246</t>
         </is>
       </c>
       <c r="D994" t="inlineStr">
         <is>
-          <t>#1 está(estão) protegido(s) de #2.</t>
+          <t>#1 treme(m) seu abdômen e libera(m) um casulo pegajoso.</t>
         </is>
       </c>
       <c r="E994" t="inlineStr">
         <is>
-          <t>#1 are/is protected.from #2.</t>
+          <t>#1 tremble(s) its abdomen and release(s) a sticky cocoon.</t>
         </is>
       </c>
       <c r="F994" t="inlineStr">
         <is>
-          <t>#1は#2から保護されている。</t>
+          <t>#1は腹を震わせ粘りつく卵塊を産み落とした。</t>
         </is>
       </c>
     </row>
     <row r="995">
       <c r="A995" t="inlineStr">
         <is>
-          <t>death_sentense</t>
+          <t>negateCondition</t>
         </is>
       </c>
       <c r="B995" t="inlineStr">
         <is>
-          <t>EA 23.261</t>
+          <t>EA 23.247</t>
         </is>
       </c>
       <c r="D995" t="inlineStr">
         <is>
-          <t>A morte abraça #1.</t>
+          <t>#1 está(estão) protegido(s) de #2.</t>
         </is>
       </c>
       <c r="E995" t="inlineStr">
         <is>
-          <t>Death embraces #1.</t>
+          <t>#1 are/is protected.from #2.</t>
         </is>
       </c>
       <c r="F995" t="inlineStr">
         <is>
-          <t>死は#1を抱きしめた。</t>
+          <t>#1は#2から保護されている。</t>
         </is>
       </c>
     </row>
     <row r="996">
       <c r="A996" t="inlineStr">
         <is>
-          <t>unseal</t>
+          <t>death_sentense</t>
         </is>
       </c>
       <c r="B996" t="inlineStr">
         <is>
-          <t>EA 23.269</t>
+          <t>EA 23.261</t>
         </is>
       </c>
       <c r="D996" t="inlineStr">
         <is>
-          <t>#1 desbloqueia #2.</t>
+          <t>A morte abraça #1.</t>
         </is>
       </c>
       <c r="E996" t="inlineStr">
         <is>
-          <t>#1 unseal(s) #2.</t>
+          <t>Death embraces #1.</t>
         </is>
       </c>
       <c r="F996" t="inlineStr">
         <is>
-          <t>#1は#2を開封した。</t>
+          <t>死は#1を抱きしめた。</t>
         </is>
       </c>
     </row>
     <row r="997">
       <c r="A997" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>unseal</t>
         </is>
       </c>
       <c r="B997" t="inlineStr">
@@ -28664,24 +28664,24 @@
       </c>
       <c r="D997" t="inlineStr">
         <is>
-          <t>Está vazio...</t>
+          <t>#1 desbloqueia #2.</t>
         </is>
       </c>
       <c r="E997" t="inlineStr">
         <is>
-          <t>It is empty...</t>
+          <t>#1 unseal(s) #2.</t>
         </is>
       </c>
       <c r="F997" t="inlineStr">
         <is>
-          <t>何も入っていなかった…</t>
+          <t>#1は#2を開封した。</t>
         </is>
       </c>
     </row>
     <row r="998">
       <c r="A998" t="inlineStr">
         <is>
-          <t>dna_loss</t>
+          <t>empty</t>
         </is>
       </c>
       <c r="B998" t="inlineStr">
@@ -28691,105 +28691,105 @@
       </c>
       <c r="D998" t="inlineStr">
         <is>
-          <t>#1 perdeu #2.</t>
+          <t>Está vazio...</t>
         </is>
       </c>
       <c r="E998" t="inlineStr">
         <is>
-          <t>#1 has lost #2.</t>
+          <t>It is empty...</t>
         </is>
       </c>
       <c r="F998" t="inlineStr">
         <is>
-          <t>#1から#2は失われた。</t>
+          <t>何も入っていなかった…</t>
         </is>
       </c>
     </row>
     <row r="999">
       <c r="A999" t="inlineStr">
         <is>
-          <t>attuned</t>
+          <t>dna_loss</t>
         </is>
       </c>
       <c r="B999" t="inlineStr">
         <is>
-          <t>EA 23.273</t>
+          <t>EA 23.269</t>
         </is>
       </c>
       <c r="D999" t="inlineStr">
         <is>
-          <t>#1 agora está sintonizado(a) com #2.</t>
+          <t>#1 perdeu #2.</t>
         </is>
       </c>
       <c r="E999" t="inlineStr">
         <is>
-          <t>#1 are/is now attuned to #2.</t>
+          <t>#1 has lost #2.</t>
         </is>
       </c>
       <c r="F999" t="inlineStr">
         <is>
-          <t>#1は#2に属化された。</t>
+          <t>#1から#2は失われた。</t>
         </is>
       </c>
     </row>
     <row r="1000">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>tender_hug</t>
+          <t>attuned</t>
         </is>
       </c>
       <c r="B1000" t="inlineStr">
         <is>
-          <t>EA 23.274</t>
+          <t>EA 23.273</t>
         </is>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
-          <t>#1 segura #2 junto a si, com extrema delicadeza.</t>
+          <t>#1 agora está sintonizado(a) com #2.</t>
         </is>
       </c>
       <c r="E1000" t="inlineStr">
         <is>
-          <t>#1 hold(s) #2 close, ever so gently.</t>
+          <t>#1 are/is now attuned to #2.</t>
         </is>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
-          <t>#1はそっと#2を抱きしめた。</t>
+          <t>#1は#2に属化された。</t>
         </is>
       </c>
     </row>
     <row r="1001">
       <c r="A1001" t="inlineStr">
         <is>
-          <t>divorce</t>
+          <t>tender_hug</t>
         </is>
       </c>
       <c r="B1001" t="inlineStr">
         <is>
-          <t>EA 23.278</t>
+          <t>EA 23.274</t>
         </is>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
-          <t>#1 se divorcia de #2.</t>
+          <t>#1 segura #2 junto a si, com extrema delicadeza.</t>
         </is>
       </c>
       <c r="E1001" t="inlineStr">
         <is>
-          <t>#1 divorce #2.</t>
+          <t>#1 hold(s) #2 close, ever so gently.</t>
         </is>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
-          <t>#1は#2と離婚した。</t>
+          <t>#1はそっと#2を抱きしめた。</t>
         </is>
       </c>
     </row>
     <row r="1002">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>married</t>
+          <t>divorce</t>
         </is>
       </c>
       <c r="B1002" t="inlineStr">
@@ -28799,44 +28799,125 @@
       </c>
       <c r="D1002" t="inlineStr">
         <is>
-          <t>#1 e #2 agora estão casados!</t>
+          <t>#1 se divorcia de #2.</t>
         </is>
       </c>
       <c r="E1002" t="inlineStr">
         <is>
-          <t>#1 and #2 are now married!</t>
+          <t>#1 divorce #2.</t>
         </is>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
-          <t>#1と#2は結婚した！</t>
+          <t>#1は#2と離婚した。</t>
         </is>
       </c>
     </row>
     <row r="1003">
       <c r="A1003" t="inlineStr">
         <is>
+          <t>married</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>EA 23.278</t>
+        </is>
+      </c>
+      <c r="D1003" t="inlineStr">
+        <is>
+          <t>#1 e #2 agora estão casados!</t>
+        </is>
+      </c>
+      <c r="E1003" t="inlineStr">
+        <is>
+          <t>#1 and #2 are now married!</t>
+        </is>
+      </c>
+      <c r="F1003" t="inlineStr">
+        <is>
+          <t>#1と#2は結婚した！</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
           <t>chu</t>
         </is>
       </c>
-      <c r="B1003" t="inlineStr">
+      <c r="B1004" t="inlineStr">
         <is>
           <t>EA 23.278</t>
         </is>
       </c>
-      <c r="D1003" t="inlineStr">
+      <c r="D1004" t="inlineStr">
         <is>
           <t>*beijo*</t>
         </is>
       </c>
-      <c r="E1003" t="inlineStr">
+      <c r="E1004" t="inlineStr">
         <is>
           <t>*kiss*</t>
         </is>
       </c>
-      <c r="F1003" t="inlineStr">
+      <c r="F1004" t="inlineStr">
         <is>
           <t>*チュッ*</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>num_little</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>EA 23.285</t>
+        </is>
+      </c>
+      <c r="D1005" t="inlineStr">
+        <is>
+          <t>Há #1 irmã(s) aqui.</t>
+        </is>
+      </c>
+      <c r="E1005" t="inlineStr">
+        <is>
+          <t>There are/is #1 little sisters/sister here.</t>
+        </is>
+      </c>
+      <c r="F1005" t="inlineStr">
+        <is>
+          <t>ここには#1人のリトルシスターがいる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>num_silvercat</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>EA 23.285</t>
+        </is>
+      </c>
+      <c r="D1006" t="inlineStr">
+        <is>
+          <t>Há #1 gato(s) prateado(s) aqui.</t>
+        </is>
+      </c>
+      <c r="E1006" t="inlineStr">
+        <is>
+          <t>There are/is #1 silver cats/cat here.</t>
+        </is>
+      </c>
+      <c r="F1006" t="inlineStr">
+        <is>
+          <t>ここには#1匹のシルバーキャットがいる。</t>
         </is>
       </c>
     </row>

--- a/PTBR/Lang/PTBR/Game/Game.xlsx
+++ b/PTBR/Lang/PTBR/Game/Game.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1006"/>
+  <dimension ref="A1:F1003"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col collapsed="1" width="16" customWidth="1" min="1" max="1"/>
@@ -23363,22 +23363,22 @@
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>EA 23.285</t>
+          <t>Alpha 20.64</t>
         </is>
       </c>
       <c r="D803" t="inlineStr">
         <is>
-          <t>#1 chicote(s) #2 com #3.</t>
+          <t xml:space="preserve"> • 「Você açoita #1 com #2」 •</t>
         </is>
       </c>
       <c r="E803" t="inlineStr">
         <is>
-          <t>#1 whip(s) #2 with #3.</t>
+          <t>You whip #1 with #2.</t>
         </is>
       </c>
       <c r="F803" t="inlineStr">
         <is>
-          <t>#1は#3で#2を打った。</t>
+          <t>あなたは#2で#1を打った。</t>
         </is>
       </c>
     </row>
@@ -28411,34 +28411,34 @@
     <row r="988">
       <c r="A988" t="inlineStr">
         <is>
-          <t>cat_migration</t>
+          <t>self_dupe</t>
         </is>
       </c>
       <c r="B988" t="inlineStr">
         <is>
-          <t>EA 23.285</t>
+          <t>EA 23.207</t>
         </is>
       </c>
       <c r="D988" t="inlineStr">
         <is>
-          <t>#1 Gato(s) Prateado(s) parte(m) em busca de um novo lar.</t>
+          <t>#1 monta(m) #2.</t>
         </is>
       </c>
       <c r="E988" t="inlineStr">
         <is>
-          <t>#1 Silver Cats/Cat depart(s) in search of a new home.</t>
+          <t>#1 assemble(s) #2.</t>
         </is>
       </c>
       <c r="F988" t="inlineStr">
         <is>
-          <t>#1匹のシルバーキャット達は新天地を求めて旅立っていった。</t>
+          <t>#1は#2を組み立てた。</t>
         </is>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="inlineStr">
         <is>
-          <t>self_dupe</t>
+          <t>update_deepest</t>
         </is>
       </c>
       <c r="B989" t="inlineStr">
@@ -28448,105 +28448,105 @@
       </c>
       <c r="D989" t="inlineStr">
         <is>
-          <t>#1 monta(m) #2.</t>
+          <t>O nível mais profundo alcançado foi atualizado para #1.</t>
         </is>
       </c>
       <c r="E989" t="inlineStr">
         <is>
-          <t>#1 assemble(s) #2.</t>
+          <t>The deepest reached level has been updated to #1.</t>
         </is>
       </c>
       <c r="F989" t="inlineStr">
         <is>
-          <t>#1は#2を組み立てた。</t>
+          <t>最深到達層が#1階に更新された。</t>
         </is>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="inlineStr">
         <is>
-          <t>update_deepest</t>
+          <t>update_deepest_void</t>
         </is>
       </c>
       <c r="B990" t="inlineStr">
         <is>
-          <t>EA 23.207</t>
+          <t>EA 23.209</t>
         </is>
       </c>
       <c r="D990" t="inlineStr">
         <is>
-          <t>O nível mais profundo alcançado foi atualizado para #1.</t>
+          <t>O nível mais profundo alcançado do Vazio foi atualizado para #1.</t>
         </is>
       </c>
       <c r="E990" t="inlineStr">
         <is>
-          <t>The deepest reached level has been updated to #1.</t>
+          <t>The deepest reached level of the Void has been updated to #1.</t>
         </is>
       </c>
       <c r="F990" t="inlineStr">
         <is>
-          <t>最深到達層が#1階に更新された。</t>
+          <t>すくつの最深到達層が#1階に更新された。</t>
         </is>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="inlineStr">
         <is>
-          <t>update_deepest_void</t>
+          <t>transform_seen</t>
         </is>
       </c>
       <c r="B991" t="inlineStr">
         <is>
-          <t>EA 23.209</t>
+          <t>EA 23.245</t>
         </is>
       </c>
       <c r="D991" t="inlineStr">
         <is>
-          <t>O nível mais profundo alcançado do Vazio foi atualizado para #1.</t>
+          <t>Alguém descobre quem #1 realmente é(são)!</t>
         </is>
       </c>
       <c r="E991" t="inlineStr">
         <is>
-          <t>The deepest reached level of the Void has been updated to #1.</t>
+          <t>Someone figures out who #1 really are/is!</t>
         </is>
       </c>
       <c r="F991" t="inlineStr">
         <is>
-          <t>すくつの最深到達層が#1階に更新された。</t>
+          <t>誰かが#1の正体に気づいた！</t>
         </is>
       </c>
     </row>
     <row r="992">
       <c r="A992" t="inlineStr">
         <is>
-          <t>transform_seen</t>
+          <t>egghatch</t>
         </is>
       </c>
       <c r="B992" t="inlineStr">
         <is>
-          <t>EA 23.245</t>
+          <t>EA 23.246</t>
         </is>
       </c>
       <c r="D992" t="inlineStr">
         <is>
-          <t>Alguém descobre quem #1 realmente é(são)!</t>
+          <t>Um casulo se abre e algo rasteja para fora.</t>
         </is>
       </c>
       <c r="E992" t="inlineStr">
         <is>
-          <t>Someone figures out who #1 really are/is!</t>
+          <t>A cocoon splits open as something crawls out.</t>
         </is>
       </c>
       <c r="F992" t="inlineStr">
         <is>
-          <t>誰かが#1の正体に気づいた！</t>
+          <t>コクーンの殻を破り何かが這い出した。</t>
         </is>
       </c>
     </row>
     <row r="993">
       <c r="A993" t="inlineStr">
         <is>
-          <t>egghatch</t>
+          <t>egglay</t>
         </is>
       </c>
       <c r="B993" t="inlineStr">
@@ -28556,105 +28556,105 @@
       </c>
       <c r="D993" t="inlineStr">
         <is>
-          <t>Um casulo se abre e algo rasteja para fora.</t>
+          <t>#1 treme(m) seu abdômen e libera(m) um casulo pegajoso.</t>
         </is>
       </c>
       <c r="E993" t="inlineStr">
         <is>
-          <t>A cocoon splits open as something crawls out.</t>
+          <t>#1 tremble(s) its abdomen and release(s) a sticky cocoon.</t>
         </is>
       </c>
       <c r="F993" t="inlineStr">
         <is>
-          <t>コクーンの殻を破り何かが這い出した。</t>
+          <t>#1は腹を震わせ粘りつく卵塊を産み落とした。</t>
         </is>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="inlineStr">
         <is>
-          <t>egglay</t>
+          <t>negateCondition</t>
         </is>
       </c>
       <c r="B994" t="inlineStr">
         <is>
-          <t>EA 23.246</t>
+          <t>EA 23.247</t>
         </is>
       </c>
       <c r="D994" t="inlineStr">
         <is>
-          <t>#1 treme(m) seu abdômen e libera(m) um casulo pegajoso.</t>
+          <t>#1 está(estão) protegido(s) de #2.</t>
         </is>
       </c>
       <c r="E994" t="inlineStr">
         <is>
-          <t>#1 tremble(s) its abdomen and release(s) a sticky cocoon.</t>
+          <t>#1 are/is protected.from #2.</t>
         </is>
       </c>
       <c r="F994" t="inlineStr">
         <is>
-          <t>#1は腹を震わせ粘りつく卵塊を産み落とした。</t>
+          <t>#1は#2から保護されている。</t>
         </is>
       </c>
     </row>
     <row r="995">
       <c r="A995" t="inlineStr">
         <is>
-          <t>negateCondition</t>
+          <t>death_sentense</t>
         </is>
       </c>
       <c r="B995" t="inlineStr">
         <is>
-          <t>EA 23.247</t>
+          <t>EA 23.261</t>
         </is>
       </c>
       <c r="D995" t="inlineStr">
         <is>
-          <t>#1 está(estão) protegido(s) de #2.</t>
+          <t>A morte abraça #1.</t>
         </is>
       </c>
       <c r="E995" t="inlineStr">
         <is>
-          <t>#1 are/is protected.from #2.</t>
+          <t>Death embraces #1.</t>
         </is>
       </c>
       <c r="F995" t="inlineStr">
         <is>
-          <t>#1は#2から保護されている。</t>
+          <t>死は#1を抱きしめた。</t>
         </is>
       </c>
     </row>
     <row r="996">
       <c r="A996" t="inlineStr">
         <is>
-          <t>death_sentense</t>
+          <t>unseal</t>
         </is>
       </c>
       <c r="B996" t="inlineStr">
         <is>
-          <t>EA 23.261</t>
+          <t>EA 23.269</t>
         </is>
       </c>
       <c r="D996" t="inlineStr">
         <is>
-          <t>A morte abraça #1.</t>
+          <t>#1 desbloqueia #2.</t>
         </is>
       </c>
       <c r="E996" t="inlineStr">
         <is>
-          <t>Death embraces #1.</t>
+          <t>#1 unseal(s) #2.</t>
         </is>
       </c>
       <c r="F996" t="inlineStr">
         <is>
-          <t>死は#1を抱きしめた。</t>
+          <t>#1は#2を開封した。</t>
         </is>
       </c>
     </row>
     <row r="997">
       <c r="A997" t="inlineStr">
         <is>
-          <t>unseal</t>
+          <t>empty</t>
         </is>
       </c>
       <c r="B997" t="inlineStr">
@@ -28664,24 +28664,24 @@
       </c>
       <c r="D997" t="inlineStr">
         <is>
-          <t>#1 desbloqueia #2.</t>
+          <t>Está vazio...</t>
         </is>
       </c>
       <c r="E997" t="inlineStr">
         <is>
-          <t>#1 unseal(s) #2.</t>
+          <t>It is empty...</t>
         </is>
       </c>
       <c r="F997" t="inlineStr">
         <is>
-          <t>#1は#2を開封した。</t>
+          <t>何も入っていなかった…</t>
         </is>
       </c>
     </row>
     <row r="998">
       <c r="A998" t="inlineStr">
         <is>
-          <t>empty</t>
+          <t>dna_loss</t>
         </is>
       </c>
       <c r="B998" t="inlineStr">
@@ -28691,105 +28691,105 @@
       </c>
       <c r="D998" t="inlineStr">
         <is>
-          <t>Está vazio...</t>
+          <t>#1 perdeu #2.</t>
         </is>
       </c>
       <c r="E998" t="inlineStr">
         <is>
-          <t>It is empty...</t>
+          <t>#1 has lost #2.</t>
         </is>
       </c>
       <c r="F998" t="inlineStr">
         <is>
-          <t>何も入っていなかった…</t>
+          <t>#1から#2は失われた。</t>
         </is>
       </c>
     </row>
     <row r="999">
       <c r="A999" t="inlineStr">
         <is>
-          <t>dna_loss</t>
+          <t>attuned</t>
         </is>
       </c>
       <c r="B999" t="inlineStr">
         <is>
-          <t>EA 23.269</t>
+          <t>EA 23.273</t>
         </is>
       </c>
       <c r="D999" t="inlineStr">
         <is>
-          <t>#1 perdeu #2.</t>
+          <t>#1 agora está sintonizado(a) com #2.</t>
         </is>
       </c>
       <c r="E999" t="inlineStr">
         <is>
-          <t>#1 has lost #2.</t>
+          <t>#1 are/is now attuned to #2.</t>
         </is>
       </c>
       <c r="F999" t="inlineStr">
         <is>
-          <t>#1から#2は失われた。</t>
+          <t>#1は#2に属化された。</t>
         </is>
       </c>
     </row>
     <row r="1000">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>attuned</t>
+          <t>tender_hug</t>
         </is>
       </c>
       <c r="B1000" t="inlineStr">
         <is>
-          <t>EA 23.273</t>
+          <t>EA 23.274</t>
         </is>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
-          <t>#1 agora está sintonizado(a) com #2.</t>
+          <t>#1 segura #2 junto a si, com extrema delicadeza.</t>
         </is>
       </c>
       <c r="E1000" t="inlineStr">
         <is>
-          <t>#1 are/is now attuned to #2.</t>
+          <t>#1 hold(s) #2 close, ever so gently.</t>
         </is>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
-          <t>#1は#2に属化された。</t>
+          <t>#1はそっと#2を抱きしめた。</t>
         </is>
       </c>
     </row>
     <row r="1001">
       <c r="A1001" t="inlineStr">
         <is>
-          <t>tender_hug</t>
+          <t>divorce</t>
         </is>
       </c>
       <c r="B1001" t="inlineStr">
         <is>
-          <t>EA 23.274</t>
+          <t>EA 23.278</t>
         </is>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
-          <t>#1 segura #2 junto a si, com extrema delicadeza.</t>
+          <t>#1 se divorcia de #2.</t>
         </is>
       </c>
       <c r="E1001" t="inlineStr">
         <is>
-          <t>#1 hold(s) #2 close, ever so gently.</t>
+          <t>#1 divorce #2.</t>
         </is>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
-          <t>#1はそっと#2を抱きしめた。</t>
+          <t>#1は#2と離婚した。</t>
         </is>
       </c>
     </row>
     <row r="1002">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>divorce</t>
+          <t>married</t>
         </is>
       </c>
       <c r="B1002" t="inlineStr">
@@ -28799,24 +28799,24 @@
       </c>
       <c r="D1002" t="inlineStr">
         <is>
-          <t>#1 se divorcia de #2.</t>
+          <t>#1 e #2 agora estão casados!</t>
         </is>
       </c>
       <c r="E1002" t="inlineStr">
         <is>
-          <t>#1 divorce #2.</t>
+          <t>#1 and #2 are now married!</t>
         </is>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
-          <t>#1は#2と離婚した。</t>
+          <t>#1と#2は結婚した！</t>
         </is>
       </c>
     </row>
     <row r="1003">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>married</t>
+          <t>chu</t>
         </is>
       </c>
       <c r="B1003" t="inlineStr">
@@ -28826,98 +28826,17 @@
       </c>
       <c r="D1003" t="inlineStr">
         <is>
-          <t>#1 e #2 agora estão casados!</t>
+          <t>*beijo*</t>
         </is>
       </c>
       <c r="E1003" t="inlineStr">
         <is>
-          <t>#1 and #2 are now married!</t>
+          <t>*kiss*</t>
         </is>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
-          <t>#1と#2は結婚した！</t>
-        </is>
-      </c>
-    </row>
-    <row r="1004">
-      <c r="A1004" t="inlineStr">
-        <is>
-          <t>chu</t>
-        </is>
-      </c>
-      <c r="B1004" t="inlineStr">
-        <is>
-          <t>EA 23.278</t>
-        </is>
-      </c>
-      <c r="D1004" t="inlineStr">
-        <is>
-          <t>*beijo*</t>
-        </is>
-      </c>
-      <c r="E1004" t="inlineStr">
-        <is>
-          <t>*kiss*</t>
-        </is>
-      </c>
-      <c r="F1004" t="inlineStr">
-        <is>
           <t>*チュッ*</t>
-        </is>
-      </c>
-    </row>
-    <row r="1005">
-      <c r="A1005" t="inlineStr">
-        <is>
-          <t>num_little</t>
-        </is>
-      </c>
-      <c r="B1005" t="inlineStr">
-        <is>
-          <t>EA 23.285</t>
-        </is>
-      </c>
-      <c r="D1005" t="inlineStr">
-        <is>
-          <t>Há #1 irmã(s) aqui.</t>
-        </is>
-      </c>
-      <c r="E1005" t="inlineStr">
-        <is>
-          <t>There are/is #1 little sisters/sister here.</t>
-        </is>
-      </c>
-      <c r="F1005" t="inlineStr">
-        <is>
-          <t>ここには#1人のリトルシスターがいる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="1006">
-      <c r="A1006" t="inlineStr">
-        <is>
-          <t>num_silvercat</t>
-        </is>
-      </c>
-      <c r="B1006" t="inlineStr">
-        <is>
-          <t>EA 23.285</t>
-        </is>
-      </c>
-      <c r="D1006" t="inlineStr">
-        <is>
-          <t>Há #1 gato(s) prateado(s) aqui.</t>
-        </is>
-      </c>
-      <c r="E1006" t="inlineStr">
-        <is>
-          <t>There are/is #1 silver cats/cat here.</t>
-        </is>
-      </c>
-      <c r="F1006" t="inlineStr">
-        <is>
-          <t>ここには#1匹のシルバーキャットがいる。</t>
         </is>
       </c>
     </row>
